--- a/dataset/Non-Faulty/unlock_without_lock.xlsx
+++ b/dataset/Non-Faulty/unlock_without_lock.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, unlock_without_lock_004_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_004_tsk_002, (void *)t2); sleep(1); #endif /* defined(CHECKER_POLYSPACE) */ } void *unlock_without_lock_004_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_004_glb_mutex_1 ); #if defined PRINT_DEBUG printf("Task4_1! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ unlock_without_lock_004_glb_var += 20; pthread_mutex_unlock( &amp;unlock_without_lock_004_glb_mutex_1 ); } i--; } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * unlock_without_lock_004_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_004_glb_mutex_2 ); /*Tool should not detect this line as error*/ /* No ERROR:UnLock without lock */ unlock_without_lock_004_glb_var += 5; pthread_mutex_unlock( &amp;unlock_without_lock_004_glb_mutex_2 ); } i--; } #if defined PRINT_DEBUG printf("Task4_2! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, unlock_without_lock_004_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_004_tsk_002, (void *)t2); sleep(1); #endif /* defined(CHECKER_POLYSPACE) */ } void * unlock_without_lock_004_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_004_glb_mutex_2 ); /*Tool should not detect this line as error*/ /* No ERROR:UnLock without lock */ unlock_without_lock_004_glb_var += 5; pthread_mutex_unlock( &amp;unlock_without_lock_004_glb_mutex_2 ); } i--; } #if defined PRINT_DEBUG printf("Task4_2! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *unlock_without_lock_004_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_004_glb_mutex_1 ); #if defined PRINT_DEBUG printf("Task4_1! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ unlock_without_lock_004_glb_var += 20; pthread_mutex_unlock( &amp;unlock_without_lock_004_glb_mutex_1 ); } i--; } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_006 () { int thread_set = 0; #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; if ( thread_set == CREATE_THREAD) { ; } else { pthread_create(&amp;th1, NULL, unlock_without_lock_006_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_006_tsk_002, (void *)t2); sleep(1); } #endif /* defined(CHECKER_POLYSPACE) */ } void * unlock_without_lock_006_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; ip = (long)input; ip = ip *20; if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_006_glb_mutex_2 ); strcpy(unlock_without_lock_006_glb_buf,"STRI"); pthread_mutex_unlock( &amp;unlock_without_lock_006_glb_mutex_2 ); } #if defined PRINT_DEBUG printf("Task6_2! Unlock without Lock, thread #%ld! buf = %s\n",ip,unlock_without_lock_006_glb_buf); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * unlock_without_lock_006_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i; ip = (long)input; ip = ip *10; for (i=0;i&lt;5;i++) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_006_glb_mutex_1 ); /*Tool should not detect this line as error*/ /* No ERROR:UnLock without lock */ unlock_without_lock_006_glb_buf[i] = 'a'; pthread_mutex_unlock( &amp;unlock_without_lock_006_glb_mutex_1 ); } } #if defined PRINT_DEBUG printf("Task6_1! Unlock without Lock, thread #%ld! buf %s\n",ip,unlock_without_lock_006_glb_buf); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_006 () { int thread_set = 0; #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; if ( thread_set == CREATE_THREAD) { ; } else { pthread_create(&amp;th1, NULL, unlock_without_lock_006_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_006_tsk_002, (void *)t2); sleep(1); } #endif /* defined(CHECKER_POLYSPACE) */ } void * unlock_without_lock_006_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i; ip = (long)input; ip = ip *10; for (i=0;i&lt;5;i++) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_006_glb_mutex_1 ); /*Tool should not detect this line as error*/ /* No ERROR:UnLock without lock */ unlock_without_lock_006_glb_buf[i] = 'a'; pthread_mutex_unlock( &amp;unlock_without_lock_006_glb_mutex_1 ); } } #if defined PRINT_DEBUG printf("Task6_1! Unlock without Lock, thread #%ld! buf %s\n",ip,unlock_without_lock_006_glb_buf); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * unlock_without_lock_006_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; ip = (long)input; ip = ip *20; if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_006_glb_mutex_2 ); strcpy(unlock_without_lock_006_glb_buf,"STRI"); pthread_mutex_unlock( &amp;unlock_without_lock_006_glb_mutex_2 ); } #if defined PRINT_DEBUG printf("Task6_2! Unlock without Lock, thread #%ld! buf = %s\n",ip,unlock_without_lock_006_glb_buf); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/unlock_without_lock.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_008 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; pthread_create(&amp;th1, NULL, unlock_without_lock_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_008_tsk_002, (void *)t2); pthread_join(th1, NULL); pthread_join(th2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void *unlock_without_lock_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_1 ); unlock_without_lock_008_glb_var += 10; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_1 ); } i--; }while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_1! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * unlock_without_lock_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_2 ); if(i!=6) { unlock_without_lock_008_glb_var += 20; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_2 );/*Tool should not detect this line as error*/ /* No ERROR:Unlock without Lock */ } } i--; } while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_2! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_008 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; pthread_create(&amp;th1, NULL, unlock_without_lock_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_008_tsk_002, (void *)t2); pthread_join(th1, NULL); pthread_join(th2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void * unlock_without_lock_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_2 ); if(i!=6) { unlock_without_lock_008_glb_var += 20; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_2 );/*Tool should not detect this line as error*/ /* No ERROR:Unlock without Lock */ } } i--; } while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_2! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *unlock_without_lock_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_1 ); unlock_without_lock_008_glb_var += 10; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_1 ); } i--; }while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_1! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
